--- a/servers/maze_main_server_dev/conf.d/data/maze_attr_list_type_v8【迷宫-属性列表-分类】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_attr_list_type_v8【迷宫-属性列表-分类】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DABC222-14D7-4609-8839-5302D19F021A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{688CBC54-A179-45F1-8A9A-2B5198D27C93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{C454262E-858A-432F-888C-7E5C3E242119}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>类型名称</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -67,6 +67,10 @@
   </si>
   <si>
     <t>基础属性</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>元素抗性</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -454,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E46EBA8-2B8D-48B5-9587-59509F01075C}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" bestFit="1" customWidth="1"/>
@@ -499,6 +503,14 @@
         <v>7</v>
       </c>
     </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server_dev/conf.d/data/maze_attr_list_type_v8【迷宫-属性列表-分类】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_attr_list_type_v8【迷宫-属性列表-分类】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{688CBC54-A179-45F1-8A9A-2B5198D27C93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DABC222-14D7-4609-8839-5302D19F021A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{C454262E-858A-432F-888C-7E5C3E242119}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>类型名称</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -67,10 +67,6 @@
   </si>
   <si>
     <t>基础属性</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>元素抗性</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -458,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E46EBA8-2B8D-48B5-9587-59509F01075C}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" bestFit="1" customWidth="1"/>
@@ -503,14 +499,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A6" s="1">
-        <v>2</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
